--- a/site/HR-to-Okta-1-1-0/headings.xlsx
+++ b/site/HR-to-Okta-1-1-0/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,28 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Known Limitations and Issues</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KKX2YY63ZKRX53RBJWVNE2S1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0/#h_01KKX2YY63ZKRX53RBJWVNE2S1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-to-Okta-1-1-0/headings.xlsx
+++ b/site/HR-to-Okta-1-1-0/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,20 +573,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01M0WFG7XVARRP6RQ68E7VS5Y2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0/#h_01M0WFG7XVARRP6RQ68E7VS5Y2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Known Limitations and Issues</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>h_01KKX2YY63ZKRX53RBJWVNE2S1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0/#h_01KKX2YY63ZKRX53RBJWVNE2S1</t>
         </is>

--- a/site/HR-to-Okta-1-1-0/headings.xlsx
+++ b/site/HR-to-Okta-1-1-0/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -611,6 +611,50 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0/#h_01KKX2YY63ZKRX53RBJWVNE2S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Integration Logs</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KYS4Z30XJ3ZBW70Z56D1J8QB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0/#h_01KYS4Z30XJ3ZBW70Z56D1J8QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01M0Y7HJTEFWWZD26WVW14YERH</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0/#h_01M0Y7HJTEFWWZD26WVW14YERH</t>
         </is>
       </c>
     </row>
